--- a/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/ホーム画面/操作仕様書.xlsx
+++ b/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/ホーム画面/操作仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjk037_\Desktop\学習用\家計管理アプリ\b_詳細設計\画面設計\ホーム画面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D5E33C-2AE3-4046-A03C-D25ACE90EE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989976D1-150F-4D96-82FC-B24F7534CC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12060" yWindow="0" windowWidth="13860" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="13860" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
   <si>
     <t>「前の月」ボタン押下</t>
     <rPh sb="1" eb="2">
@@ -271,25 +271,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>新情報作成画面へ遷移</t>
-    <rPh sb="0" eb="1">
-      <t>シン</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>個別収支カードをクリック</t>
     <rPh sb="0" eb="2">
       <t>コベツ</t>
@@ -342,77 +323,118 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カードのhomeruフラグを更新する。フラグはnumber型で制御され、</t>
-    <rPh sb="14" eb="16">
+    <t>PUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/index/homeru/${id}</t>
+  </si>
+  <si>
+    <t>実行API</t>
+    <rPh sb="0" eb="2">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新情報作成画面へ遷移。</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同時に画面上でもkakeiboDTOのフラグを更新し、</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
       <t>コウシン</t>
     </rPh>
-    <rPh sb="29" eb="30">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>セイギョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1ならば赤いハート、0ならば灰色のハートが表示される。</t>
-    <rPh sb="4" eb="5">
-      <t>アカ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ハイイロ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>homeruフラグを1-0で切り替える。１がアクティブ、0がネガティブ（初期値）。</t>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>ショキチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これによって該当カード上のハートの表示を切り替え、</t>
+    <rPh sb="6" eb="8">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>これと同時に月間のhomeruの総数も再計算され、</t>
-    <rPh sb="3" eb="5">
-      <t>ドウジ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ゲッカン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>また該当月間のがんばった総数の変化により「がんばった」数の」ハート総数も更新する</t>
+    <rPh sb="2" eb="6">
+      <t>ガイトウゲッカン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
       <t>ソウスウ</t>
     </rPh>
-    <rPh sb="19" eb="22">
-      <t>サイケイサン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>homeru=1の数だけ「頑張った数」欄にハートが並ぶ</t>
-    <rPh sb="9" eb="10">
+    <rPh sb="15" eb="17">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
       <t>カズ</t>
     </rPh>
-    <rPh sb="13" eb="15">
-      <t>ガンバ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カズ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ナラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PUT</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>http://localhost:8080/index/homeru/${id}</t>
-  </si>
-  <si>
-    <t>実行API</t>
-    <rPh sb="0" eb="2">
-      <t>ジッコウ</t>
+    <rPh sb="33" eb="35">
+      <t>ソウスウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カード上のハートマークをクリックすることで、kakeiboテーブルにおける該当id収支の</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>シュウシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -826,7 +848,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EF517BB-9F64-4577-AC59-118E43ACFF5F}">
-  <dimension ref="A2:E38"/>
+  <dimension ref="A2:E39"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="21.375" bestFit="1" customWidth="1"/>
@@ -891,12 +913,12 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
@@ -939,12 +961,12 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" t="s">
         <v>17</v>
       </c>
     </row>
@@ -983,7 +1005,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1002,7 +1024,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
@@ -1011,7 +1033,7 @@
         <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1021,7 +1043,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1038,21 +1060,21 @@
         <v>11</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1062,22 +1084,27 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>29</v>
+      <c r="A37" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
